--- a/public/templates/template_import_guru.xlsx
+++ b/public/templates/template_import_guru.xlsx
@@ -2,52 +2,38 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alsya\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E9EEFEF-3DD5-4DA3-8C59-B4715F16AD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532A33BC-CEB1-4EC3-93E1-FE7FB051AB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8100F12E-0F68-4BAD-8A25-48DA69C71962}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="DATA GURU" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>nik</t>
   </si>
   <si>
+    <t>nama_lengkap</t>
+  </si>
+  <si>
     <t>nip</t>
   </si>
   <si>
     <t>nuptk</t>
   </si>
   <si>
-    <t>nama_lengkap</t>
-  </si>
-  <si>
     <t>tempat_lahir</t>
   </si>
   <si>
@@ -75,6 +61,15 @@
     <t>mata_pelajaran</t>
   </si>
   <si>
+    <t>tmt_sk</t>
+  </si>
+  <si>
+    <t>mkg_tahun</t>
+  </si>
+  <si>
+    <t>mkg_bulan</t>
+  </si>
+  <si>
     <t>pendidikan_terakhir</t>
   </si>
   <si>
@@ -84,69 +79,116 @@
     <t>nrg</t>
   </si>
   <si>
-    <t>351501...</t>
-  </si>
-  <si>
-    <t>198501...</t>
-  </si>
-  <si>
-    <t>123456...</t>
-  </si>
-  <si>
-    <t>Budi Santoso</t>
+    <t>3515011009920001</t>
+  </si>
+  <si>
+    <t>Ahmad Subagja, S.Pd.</t>
+  </si>
+  <si>
+    <t>199209102022011001</t>
+  </si>
+  <si>
+    <t>1234567890123456</t>
+  </si>
+  <si>
+    <t>Jakarta</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Sri Wahyuni</t>
+  </si>
+  <si>
+    <t>PNS</t>
+  </si>
+  <si>
+    <t>III/a</t>
+  </si>
+  <si>
+    <t>Guru Ahli Pertama</t>
+  </si>
+  <si>
+    <t>Guru Kelas</t>
+  </si>
+  <si>
+    <t>Guru Kelas 4</t>
+  </si>
+  <si>
+    <t>S-1</t>
+  </si>
+  <si>
+    <t>3515022005950002</t>
+  </si>
+  <si>
+    <t>Siti Rahmawati, S.Pd.</t>
+  </si>
+  <si>
+    <t>1234567890123457</t>
+  </si>
+  <si>
+    <t>Sidoarjo</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>Khadijah</t>
+  </si>
+  <si>
+    <t>PPPK</t>
+  </si>
+  <si>
+    <t>IX</t>
+  </si>
+  <si>
+    <t>Guru Kelas 1</t>
+  </si>
+  <si>
+    <t>3515033008980003</t>
+  </si>
+  <si>
+    <t>Budi Santoso, S.Pd.</t>
   </si>
   <si>
     <t>Surabaya</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>Siti Aminah</t>
   </si>
   <si>
-    <t>PNS</t>
-  </si>
-  <si>
-    <t>III/a</t>
-  </si>
-  <si>
-    <t>Guru Kelas</t>
-  </si>
-  <si>
-    <t>Tematik</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>-</t>
+    <t>GTT</t>
+  </si>
+  <si>
+    <t>Guru Mata Pelajaran</t>
+  </si>
+  <si>
+    <t>Guru Mapel</t>
+  </si>
+  <si>
+    <t>PJOK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -169,18 +211,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -199,150 +233,56 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -485,33 +425,18 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A417E515-3A35-4111-97F8-C7DD457CEB35}">
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="28.26953125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.90625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.90625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.6328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.54296875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="22" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22.81640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="23.453125" style="2" customWidth="1"/>
-    <col min="10" max="16" width="22" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="8.7265625" style="2"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:S4"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,55 +485,167 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" ht="28" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="4">
-        <v>31048</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="F2" s="2">
+        <v>33857</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="J2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="2">
+        <v>44562</v>
+      </c>
+      <c r="O2" s="1">
+        <v>2</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="1">
+        <v>88900123</v>
+      </c>
+      <c r="S2" s="1">
+        <v>77123456</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2">
+        <v>34839</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" s="2">
+        <v>45078</v>
+      </c>
+      <c r="O3" s="1">
+        <v>1</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="2">
+        <v>36022</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="2">
+        <v>44392</v>
+      </c>
+      <c r="O4" s="1">
+        <v>3</v>
+      </c>
+      <c r="P4" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
